--- a/data/trans_bre/IP2004-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP2004-Habitat-trans_bre.xlsx
@@ -660,37 +660,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,21; 3,52</t>
+          <t>-3,27; 3,49</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,39; 2,78</t>
+          <t>-5,86; 2,69</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 6,95</t>
+          <t>-2,1; 6,83</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,22; -0,65</t>
+          <t>-6,28; -0,68</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-68,09; 200,88</t>
+          <t>-67,0; 175,5</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-81,24; 137,95</t>
+          <t>-82,72; 123,17</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-57,45; 752,64</t>
+          <t>-67,06; 599,99</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 4,31</t>
+          <t>-2,45; 3,94</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 3,51</t>
+          <t>-1,27; 3,38</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 2,86</t>
+          <t>-1,07; 3,03</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-3,03; 2,47</t>
+          <t>-2,74; 2,76</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-46,34; 206,92</t>
+          <t>-51,88; 169,72</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-48,07; 529,58</t>
+          <t>-57,63; 424,36</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-63,11; 828,03</t>
+          <t>-61,59; 738,68</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-75,81; 188,01</t>
+          <t>-68,77; 256,35</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 4,14</t>
+          <t>-3,02; 3,89</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,54; 3,05</t>
+          <t>-2,16; 3,17</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 4,11</t>
+          <t>-0,82; 3,95</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,26; 0,6</t>
+          <t>-3,16; 0,64</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-61,38; 241,17</t>
+          <t>-69,39; 238,28</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 874,21</t>
+          <t>-90,18; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-68,04; —</t>
+          <t>-64,46; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 149,04</t>
         </is>
       </c>
     </row>
@@ -960,37 +960,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,66; 2,55</t>
+          <t>-2,66; 2,62</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 5,73</t>
+          <t>-0,98; 5,41</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 3,65</t>
+          <t>-1,23; 3,56</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,63; 0,97</t>
+          <t>-3,47; 1,09</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-82,51; 236,56</t>
+          <t>-76,69; 301,63</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-36,59; 526,28</t>
+          <t>-44,91; 497,75</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-61,61; 797,7</t>
+          <t>-67,69; 803,84</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 1,86</t>
+          <t>-1,32; 1,82</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 2,15</t>
+          <t>-1,01; 2,26</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 2,59</t>
+          <t>-0,03; 2,56</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 0,12</t>
+          <t>-2,31; 0,07</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-34,82; 78,06</t>
+          <t>-35,41; 73,28</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-27,86; 113,67</t>
+          <t>-32,31; 126,16</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-13,18; 229,47</t>
+          <t>-4,7; 229,02</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-78,1; 14,18</t>
+          <t>-77,8; 12,29</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP2004-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP2004-Habitat-trans_bre.xlsx
@@ -660,37 +660,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,27; 3,49</t>
+          <t>-3,62; 3,06</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,86; 2,69</t>
+          <t>-5,1; 3,19</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 6,83</t>
+          <t>-1,98; 6,27</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,28; -0,68</t>
+          <t>-5,75; -0,65</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-67,0; 175,5</t>
+          <t>-72,08; 153,93</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-82,72; 123,17</t>
+          <t>-77,89; 174,17</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-67,06; 599,99</t>
+          <t>-62,28; 655,24</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 3,94</t>
+          <t>-2,35; 4,31</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 3,38</t>
+          <t>-1,19; 3,19</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 3,03</t>
+          <t>-1,13; 2,83</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-2,74; 2,76</t>
+          <t>-2,67; 2,86</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-51,88; 169,72</t>
+          <t>-46,78; 219,45</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-57,63; 424,36</t>
+          <t>-52,42; 409,08</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-61,59; 738,68</t>
+          <t>-59,91; 576,35</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-68,77; 256,35</t>
+          <t>-69,13; 281,9</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,02; 3,89</t>
+          <t>-2,74; 4,12</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 3,17</t>
+          <t>-2,19; 3,35</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 3,95</t>
+          <t>-0,79; 4,13</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,16; 0,64</t>
+          <t>-3,37; 0,55</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-69,39; 238,28</t>
+          <t>-63,86; 304,92</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-90,18; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-64,46; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 149,04</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -960,37 +960,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,66; 2,62</t>
+          <t>-2,72; 2,43</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 5,41</t>
+          <t>-1,18; 5,5</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 3,56</t>
+          <t>-1,37; 3,33</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,47; 1,09</t>
+          <t>-3,7; 0,91</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-76,69; 301,63</t>
+          <t>-80,53; 262,19</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-44,91; 497,75</t>
+          <t>-40,06; 570,88</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-67,69; 803,84</t>
+          <t>-75,51; 747,04</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 1,82</t>
+          <t>-1,21; 1,8</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 2,26</t>
+          <t>-0,82; 2,32</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,03; 2,56</t>
+          <t>-0,11; 2,65</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,31; 0,07</t>
+          <t>-2,39; 0,18</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-35,41; 73,28</t>
+          <t>-33,81; 71,87</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-32,31; 126,16</t>
+          <t>-24,56; 129,53</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-4,7; 229,02</t>
+          <t>-8,03; 252,36</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-77,8; 12,29</t>
+          <t>-77,15; 24,01</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP2004-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP2004-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-2,41</t>
+          <t>-2,44</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -660,37 +660,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,62; 3,06</t>
+          <t>-3,21; 3,52</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,1; 3,19</t>
+          <t>-5,39; 2,78</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,98; 6,27</t>
+          <t>-2,11; 6,95</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,75; -0,65</t>
+          <t>-6,51; -0,63</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-72,08; 153,93</t>
+          <t>-68,09; 200,88</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-77,89; 174,17</t>
+          <t>-81,24; 137,95</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-62,28; 655,24</t>
+          <t>-57,45; 752,64</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-0,11</t>
+          <t>0,3</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-4,06%</t>
+          <t>11,53%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,35; 4,31</t>
+          <t>-2,26; 4,31</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 3,19</t>
+          <t>-1,22; 3,51</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 2,83</t>
+          <t>-1,37; 2,86</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-2,67; 2,86</t>
+          <t>-2,47; 3,17</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-46,78; 219,45</t>
+          <t>-46,34; 206,92</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-52,42; 409,08</t>
+          <t>-48,07; 529,58</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-59,91; 576,35</t>
+          <t>-63,11; 828,03</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-69,13; 281,9</t>
+          <t>-71,06; 233,82</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-1,03</t>
+          <t>-1,04</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-55,75%</t>
+          <t>-51,7%</t>
         </is>
       </c>
     </row>
@@ -860,37 +860,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,74; 4,12</t>
+          <t>-2,49; 4,14</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,19; 3,35</t>
+          <t>-2,54; 3,05</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 4,13</t>
+          <t>-0,87; 4,11</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,37; 0,55</t>
+          <t>-3,58; 0,88</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-63,86; 304,92</t>
+          <t>-61,38; 241,17</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>-100,0; 874,21</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-68,04; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-1,27</t>
+          <t>-1,23</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-63,8%</t>
+          <t>-62,09%</t>
         </is>
       </c>
     </row>
@@ -960,37 +960,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,72; 2,43</t>
+          <t>-2,66; 2,55</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 5,5</t>
+          <t>-0,73; 5,73</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 3,33</t>
+          <t>-1,13; 3,65</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,7; 0,91</t>
+          <t>-3,62; 0,99</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-80,53; 262,19</t>
+          <t>-82,51; 236,56</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-40,06; 570,88</t>
+          <t>-36,59; 526,28</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-75,51; 747,04</t>
+          <t>-61,61; 797,7</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-1,12</t>
+          <t>-0,99</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-48,9%</t>
+          <t>-43,49%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 1,8</t>
+          <t>-1,33; 1,86</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 2,32</t>
+          <t>-0,77; 2,15</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 2,65</t>
+          <t>-0,18; 2,59</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,39; 0,18</t>
+          <t>-2,28; 0,29</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-33,81; 71,87</t>
+          <t>-34,82; 78,06</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-24,56; 129,53</t>
+          <t>-27,86; 113,67</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-8,03; 252,36</t>
+          <t>-13,18; 229,47</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-77,15; 24,01</t>
+          <t>-76,07; 24,91</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP2004-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP2004-Habitat-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,195 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>-0,15</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-1,12</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1,9</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-2,44</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-4,0%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-24,9%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>67,43%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>-0.1455020493002349</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-1.122603399225375</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>1.900240559835762</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>-2.436846665665958</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>-0.04002372899535898</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>-0.2489987398688716</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>0.6742522846787204</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-3,21; 3,52</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-5,39; 2,78</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-2,11; 6,95</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-6,51; -0,63</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-68,09; 200,88</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-81,24; 137,95</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-57,45; 752,64</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-3.213110179775963</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-5.394323840988347</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-2.10981572625468</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-6.514432932318097</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.6809262900495821</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.8124403843335427</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>-0.5744642756763234</v>
+      </c>
+      <c r="J5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>3.51789231987247</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>2.776199667284708</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>6.945952834722615</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>-0.6322431450071283</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>2.008799617585208</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>1.379541782682825</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>7.526360658556414</v>
+      </c>
+      <c r="J6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>10-50.000 hab</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>0,91</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>0,92</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>0,86</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>0,3</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>25,06%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>52,78%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>64,44%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>11,53%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-2,26; 4,31</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-1,22; 3,51</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-1,37; 2,86</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-2,47; 3,17</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-46,34; 206,92</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-48,07; 529,58</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-63,11; 828,03</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-71,06; 233,82</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>0.9072404831762769</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.9223532472543199</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.8606726525916498</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>0.2971778115416428</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0.2506065988860828</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>0.5278247440337396</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>0.6443912840016527</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>0.1153046437420686</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>&gt;50.000 hab</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>0,55</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>0,4</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>1,36</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-1,04</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>17,04%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>24,53%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>114,18%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>-51,7%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-2.257805409542334</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-1.219694787877743</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-1.366530169747731</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-2.465173624628797</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.4633930514150942</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.4807144804680945</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.6310850555978188</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.7105597206081877</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-2,49; 4,14</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-2,54; 3,05</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-0,87; 4,11</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-3,58; 0,88</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-61,38; 241,17</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 874,21</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-68,04; —</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>4.312648622943596</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>3.512537473927605</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>2.857492987327472</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>3.165393212661176</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>2.069165662261523</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>5.295836832503885</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>8.280253825444287</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>2.338195992498623</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Capitales</t>
+          <t>&gt;50.000 hab</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,197 +815,287 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-0,18</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>2,04</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>0,96</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-1,23</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-8,0%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>88,29%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>65,51%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-62,09%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>0.5517684524231576</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.4009659908820445</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>1.359006649798406</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-1.035436961707756</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>0.1703701825301815</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>0.2453257232918705</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>1.141789943045008</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>-0.5169600735490126</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-2,66; 2,55</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-0,73; 5,73</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-1,13; 3,65</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-3,62; 0,99</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-82,51; 236,56</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-36,59; 526,28</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-61,61; 797,7</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-2.493212642890948</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-2.544936756004336</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-0.8697965573366282</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-3.57998667354492</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.6137732825243017</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-0.6804241839647717</v>
+      </c>
+      <c r="J11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>4.143651536255952</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>3.049367526198206</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>4.112491651293104</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>0.8815301345172508</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>2.411726045147196</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>8.742147564762101</v>
+      </c>
+      <c r="I12" s="6" t="inlineStr"/>
+      <c r="J12" s="6" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>-0.1844942111812194</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>2.036694942057922</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.9636041541625756</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>-1.226557418051004</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.08004452142735709</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>0.8829186154833362</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>0.6550875613058296</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>-0.6209135125228255</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-2.657525179071938</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-0.7263657603632597</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-1.129692876756875</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-3.622855653361979</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.8250549894811731</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.3659405222541208</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.6160977843730577</v>
+      </c>
+      <c r="J14" s="6" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>2.552546729655681</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>5.734725674334093</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>3.645634446339434</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>0.9865817539360241</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>2.365622433839091</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>5.262760913787048</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>7.976970322944706</v>
+      </c>
+      <c r="J15" s="6" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>0,26</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>0,73</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>1,19</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-0,99</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>8,3%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>29,79%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>72,81%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>-43,49%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-1,33; 1,86</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-0,77; 2,15</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-0,18; 2,59</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-2,28; 0,29</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-34,82; 78,06</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-27,86; 113,67</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-13,18; 229,47</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-76,07; 24,91</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>0.2628764582646014</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.7262272942149459</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>1.189309266810171</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>-0.9860163449720621</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>0.08304144455482446</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>0.2978593811239766</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>0.7281006934068505</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>-0.4348543829021261</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-1.332439225733758</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-0.7687160474182222</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-0.1768790824133249</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-2.281339853793956</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.3482201138500999</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.2786012847452998</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>-0.1317998919663743</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>-0.7606903478589344</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>1.857948693066783</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>2.149107267995875</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>2.593970723103002</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>0.292869703831217</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>0.7805517430739226</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>1.136653626205526</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>2.294659853369024</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>0.2491153656959051</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1108,14 +1103,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
